--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_37.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2388899.266419166</v>
+        <v>2389970.39013144</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031954</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031956</v>
+        <v>14697842.82031954</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984940993</v>
+        <v>657188.6984940944</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984940993</v>
+        <v>657188.6984940944</v>
       </c>
     </row>
     <row r="11">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557366</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
@@ -666,13 +666,13 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>6.688316575839224</v>
+        <v>6.688316575840247</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>3.347322035758185</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.810231567849018</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -781,16 +781,16 @@
         <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.6519859716246</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.48881128536602</v>
       </c>
       <c r="T3" t="n">
-        <v>4.473444462796863</v>
+        <v>4.473444462796834</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>353.2987841991915</v>
+        <v>322.1668072190265</v>
       </c>
     </row>
     <row r="4">
@@ -848,10 +848,10 @@
         <v>91.79905402550071</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>143.0380916651275</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.4472689970477</v>
       </c>
       <c r="P4" t="n">
         <v>265.2018645413922</v>
@@ -906,7 +906,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>5.146009903586449</v>
+        <v>3.34732203575993</v>
       </c>
       <c r="H5" t="n">
         <v>3.81023156784903</v>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S5" t="n">
         <v>85.50414770182039</v>
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -982,16 +982,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>6.314974442936713</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>175.4395814561819</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1213,16 +1213,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>153.1291859623778</v>
       </c>
       <c r="S9" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T9" t="n">
         <v>4.473444462796863</v>
@@ -1267,10 +1267,10 @@
         <v>0.1959257979225981</v>
       </c>
       <c r="V9" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>156.6317311173201</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1380,7 +1380,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H11" t="n">
         <v>73.89995518593948</v>
@@ -1428,7 +1428,7 @@
         <v>310.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>319.3734759809475</v>
+        <v>318.6773909844526</v>
       </c>
       <c r="X11" t="n">
         <v>273.2818334606677</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>216.1853001651792</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>23.67209722191262</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.2619859716246</v>
+        <v>402.2042587319003</v>
       </c>
       <c r="S12" t="n">
         <v>132.901311285366</v>
@@ -1501,19 +1501,19 @@
         <v>83.17594446279683</v>
       </c>
       <c r="U12" t="n">
-        <v>81.1584257979226</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V12" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3.305168319657098</v>
+        <v>3.305168319656873</v>
       </c>
       <c r="M13" t="n">
         <v>97.89093927140236</v>
@@ -1611,13 +1611,13 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E14" t="n">
-        <v>84.66720461037373</v>
+        <v>85.36328960686865</v>
       </c>
       <c r="F14" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H14" t="n">
         <v>73.89995518593946</v>
@@ -1684,7 +1684,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>28.93768689770263</v>
@@ -1741,13 +1741,13 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V15" t="n">
-        <v>318.4529399517954</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W15" t="n">
-        <v>113.3731429098285</v>
+        <v>336.3154156701044</v>
       </c>
       <c r="X15" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
         <v>399.3913927661343</v>
@@ -1790,7 +1790,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6.155529797123449</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M16" t="n">
         <v>97.89093927140237</v>
@@ -1811,7 +1811,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588095</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1851,7 +1851,7 @@
         <v>85.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>85.88962870801186</v>
+        <v>85.19354371151695</v>
       </c>
       <c r="G17" t="n">
         <v>83.28199540259408</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T17" t="n">
         <v>261.2171194170061</v>
@@ -1921,16 +1921,16 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>265.042185205795</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>5.950139648612264</v>
@@ -1978,16 +1978,16 @@
         <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W18" t="n">
-        <v>113.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3.305168319657098</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M19" t="n">
         <v>97.89093927140237</v>
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>82.58591040609919</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593946</v>
+        <v>73.89995518593948</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
         <v>23.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279685</v>
+        <v>83.17594446279683</v>
       </c>
       <c r="U21" t="n">
-        <v>81.15842579792258</v>
+        <v>81.1584257979226</v>
       </c>
       <c r="V21" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>336.3154156701039</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>100.8627394453875</v>
+        <v>323.8050122056632</v>
       </c>
       <c r="Y21" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="22">
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588095</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>83.28199540259408</v>
       </c>
       <c r="H23" t="n">
-        <v>73.20387018947791</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.331479092594236e-11</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.2280170485541</v>
@@ -2382,7 +2382,7 @@
         <v>273.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>192.3174326828064</v>
+        <v>191.6213476863115</v>
       </c>
     </row>
     <row r="24">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>288.4988294066021</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F24" t="n">
         <v>20.63624233787687</v>
@@ -2458,10 +2458,10 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>100.8627394453875</v>
+        <v>323.805012205663</v>
       </c>
       <c r="Y24" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2513,7 +2513,7 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P25" t="n">
-        <v>285.5554374901554</v>
+        <v>288.4057989676218</v>
       </c>
       <c r="Q25" t="n">
         <v>351.422266425598</v>
@@ -2522,7 +2522,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>141.5319320520589</v>
+        <v>141.5319320520674</v>
       </c>
       <c r="T26" t="n">
         <v>261.2171194170061</v>
@@ -2629,7 +2629,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>288.498829406602</v>
       </c>
       <c r="C27" t="n">
         <v>42.09991244551929</v>
@@ -2644,10 +2644,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S27" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U27" t="n">
-        <v>81.1584257979226</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V27" t="n">
-        <v>95.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>336.3154156701044</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y27" t="n">
-        <v>399.3913927661343</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="28">
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319656873</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2756,10 +2756,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S28" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040610756</v>
       </c>
       <c r="H29" t="n">
         <v>73.89995518593948</v>
@@ -2844,7 +2844,7 @@
         <v>261.2171194170061</v>
       </c>
       <c r="U29" t="n">
-        <v>329.4071814013618</v>
+        <v>330.1032663978569</v>
       </c>
       <c r="V29" t="n">
         <v>310.8510241668239</v>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
-        <v>265.042185205795</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G30" t="n">
         <v>5.950139648612248</v>
@@ -2932,7 +2932,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>100.8627394453875</v>
+        <v>323.805012205663</v>
       </c>
       <c r="Y30" t="n">
         <v>80.39139276613435</v>
@@ -2996,7 +2996,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S31" t="n">
-        <v>28.98969199588089</v>
+        <v>28.98969199588116</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>141.5319320520589</v>
+        <v>141.5319320520674</v>
       </c>
       <c r="T32" t="n">
         <v>261.2171194170061</v>
@@ -3106,7 +3106,7 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>265.042185205795</v>
+        <v>265.0421852057948</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>3.305168319657773</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M34" t="n">
-        <v>97.89093927140236</v>
+        <v>95.04057779393607</v>
       </c>
       <c r="N34" t="n">
         <v>150.9111244520127</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>60.92708723799848</v>
+        <v>60.92708723800681</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>233.8955915313904</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>259.1497237429039</v>
+        <v>374</v>
       </c>
       <c r="X36" t="n">
-        <v>374</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>374</v>
+        <v>2.391392766134345</v>
       </c>
     </row>
     <row r="37">
@@ -3513,7 +3513,7 @@
         <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
-        <v>1.981065592038484</v>
+        <v>1.981065592046868</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>64.22801704855405</v>
+        <v>64.22801704855408</v>
       </c>
       <c r="T38" t="n">
         <v>183.2171194170061</v>
@@ -3577,16 +3577,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>312.6845221476588</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,19 +3622,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>374</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S39" t="n">
-        <v>54.90131128536602</v>
+        <v>54.90131128536603</v>
       </c>
       <c r="T39" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U39" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V39" t="n">
         <v>17.51066719152016</v>
@@ -3643,7 +3643,7 @@
         <v>35.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>22.86273944538755</v>
+        <v>179.9366330496809</v>
       </c>
       <c r="Y39" t="n">
         <v>2.391392766134345</v>
@@ -3689,10 +3689,10 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N40" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O40" t="n">
         <v>149.9026788331133</v>
@@ -3704,7 +3704,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>79.52595155468148</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3786,25 +3786,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>163.4435047435215</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>356.1032663978569</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -3829,10 +3829,10 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>31.95013964861226</v>
+        <v>31.95013964861225</v>
       </c>
       <c r="H42" t="n">
-        <v>31.54418152604376</v>
+        <v>33.93095497147735</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.386773445425144</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>205.2619859716245</v>
+        <v>205.2619859716246</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>253.9026788331133</v>
@@ -3941,10 +3941,10 @@
         <v>374</v>
       </c>
       <c r="R43" t="n">
-        <v>2.581873503943012</v>
+        <v>121.6529444826083</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -3987,10 +3987,10 @@
         <v>111.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1.919971285700395</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593948</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>101.6487042546154</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
         <v>336.8510241668239</v>
@@ -4069,7 +4069,7 @@
         <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>31.54418152604377</v>
+        <v>33.93095497147735</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445425144</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716246</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.581873503942997</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>176.9111244520127</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.581873503942618</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.7310038072329</v>
+        <v>108.7310038072321</v>
       </c>
       <c r="C2" t="n">
-        <v>58.75668234966326</v>
+        <v>58.75668234966251</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324933</v>
+        <v>48.31309069324858</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398807</v>
+        <v>43.90572745398732</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>37.14985212485576</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.76871875540305</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>400.18</v>
+        <v>29.92</v>
       </c>
       <c r="K2" t="n">
-        <v>451.8183303517587</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L2" t="n">
-        <v>515.8802453266331</v>
+        <v>385.22</v>
       </c>
       <c r="M2" t="n">
-        <v>886.1402453266331</v>
+        <v>755.48</v>
       </c>
       <c r="N2" t="n">
-        <v>1256.400245326633</v>
+        <v>1125.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1256.400245326633</v>
+        <v>1125.74</v>
       </c>
       <c r="P2" t="n">
-        <v>1314.492137192891</v>
+        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4354,19 +4354,19 @@
         <v>1222.884106610596</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>971.178558602</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>739.0058069183394</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>498.2245180486954</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>304.0004438460007</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>191.5585926512468</v>
       </c>
     </row>
     <row r="3">
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3343126211507</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="C3" t="n">
-        <v>722.3343126211507</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="D3" t="n">
-        <v>722.3343126211507</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="E3" t="n">
         <v>376.2008810838653</v>
@@ -4427,25 +4427,25 @@
         <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1151.339064143016</v>
       </c>
       <c r="T3" t="n">
         <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1146.622528526128</v>
+        <v>769.0426555947367</v>
       </c>
       <c r="V3" t="n">
-        <v>1131.965288938734</v>
+        <v>754.3854160073427</v>
       </c>
       <c r="W3" t="n">
-        <v>1099.265144585372</v>
+        <v>721.6852716539805</v>
       </c>
       <c r="X3" t="n">
-        <v>1079.201771408213</v>
+        <v>701.6218984768213</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3343126211507</v>
+        <v>376.2008810838653</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1359.924714679384</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="C4" t="n">
-        <v>1359.924714679384</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="D4" t="n">
-        <v>1359.924714679384</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="E4" t="n">
-        <v>1359.924714679384</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="F4" t="n">
-        <v>1359.924714679384</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="G4" t="n">
-        <v>1359.924714679384</v>
+        <v>853.7180055872677</v>
       </c>
       <c r="H4" t="n">
-        <v>1359.924714679384</v>
+        <v>1024.853581566337</v>
       </c>
       <c r="I4" t="n">
-        <v>1359.924714679384</v>
+        <v>1251.462556240125</v>
       </c>
       <c r="J4" t="n">
-        <v>1360.719007775399</v>
+        <v>1251.462556240125</v>
       </c>
       <c r="K4" t="n">
-        <v>1492.239579417185</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L4" t="n">
-        <v>1496</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="M4" t="n">
-        <v>1403.273682802524</v>
+        <v>1294.017231267251</v>
       </c>
       <c r="N4" t="n">
-        <v>1258.790761928658</v>
+        <v>1149.534310393385</v>
       </c>
       <c r="O4" t="n">
-        <v>1042.177358901337</v>
+        <v>932.9209073660643</v>
       </c>
       <c r="P4" t="n">
-        <v>774.2966876474056</v>
+        <v>665.0402361121328</v>
       </c>
       <c r="Q4" t="n">
-        <v>460.7236912579127</v>
+        <v>351.4672397226398</v>
       </c>
       <c r="R4" t="n">
-        <v>139.176451535273</v>
+        <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>179.6001272851838</v>
+        <v>70.34367574991083</v>
       </c>
       <c r="T4" t="n">
-        <v>368.4538490669395</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>615.0149741642425</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V4" t="n">
-        <v>813.8363670501885</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W4" t="n">
-        <v>985.7272853098659</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="X4" t="n">
-        <v>1136.75807633406</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="Y4" t="n">
-        <v>1248.167377013092</v>
+        <v>704.5799155149155</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G5" t="n">
         <v>33.76871875540306</v>
@@ -4558,19 +4558,19 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L5" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M5" t="n">
-        <v>327.128108133742</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>697.388108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O5" t="n">
         <v>1067.648108133742</v>
@@ -4582,28 +4582,28 @@
         <v>1496</v>
       </c>
       <c r="R5" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="6">
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>719.1203429896864</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C6" t="n">
-        <v>719.1203429896864</v>
+        <v>711.2404154681431</v>
       </c>
       <c r="D6" t="n">
-        <v>719.1203429896864</v>
+        <v>711.2404154681431</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>365.1069839308576</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>365.1069839308576</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>36.29876206357244</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>36.29876206357244</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4661,28 +4661,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>968.469334165078</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>791.2576357244901</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>786.7390049539882</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>786.5411001076018</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>771.8838605202077</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>739.1837161668456</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X6" t="n">
-        <v>719.1203429896864</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>719.1203429896864</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>575.7683720264802</v>
+        <v>143.2391441250001</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264802</v>
+        <v>205.5083720264802</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184156</v>
+        <v>329.8693446184157</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872682</v>
+        <v>483.4580055872682</v>
       </c>
       <c r="H7" t="n">
-        <v>1024.853581566338</v>
+        <v>654.5935815663379</v>
       </c>
       <c r="I7" t="n">
-        <v>1251.462556240126</v>
+        <v>881.2025562401257</v>
       </c>
       <c r="J7" t="n">
         <v>1251.462556240126</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>505.7585226289696</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>575.7683720264802</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4795,19 +4795,19 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>81.5583303517588</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>145.6202453266332</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>327.128108133742</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>697.388108133742</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
         <v>1067.648108133742</v>
@@ -4819,7 +4819,7 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S8" t="n">
         <v>1407.815317606417</v>
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.92</v>
+        <v>1056.313862392149</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>1056.313862392149</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>704.8616534045707</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>358.7282218672851</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4898,28 +4898,28 @@
         <v>1346.247111942856</v>
       </c>
       <c r="R9" t="n">
-        <v>968.469334165078</v>
+        <v>1191.571166526312</v>
       </c>
       <c r="S9" t="n">
-        <v>590.6915563873001</v>
+        <v>1128.451155126953</v>
       </c>
       <c r="T9" t="n">
-        <v>586.1729256167982</v>
+        <v>1123.932524356451</v>
       </c>
       <c r="U9" t="n">
-        <v>585.9750207704118</v>
+        <v>1123.734619510064</v>
       </c>
       <c r="V9" t="n">
-        <v>208.197242992634</v>
+        <v>1109.07737992267</v>
       </c>
       <c r="W9" t="n">
-        <v>49.98337317715914</v>
+        <v>1076.377235569308</v>
       </c>
       <c r="X9" t="n">
-        <v>29.92</v>
+        <v>1056.313862392149</v>
       </c>
       <c r="Y9" t="n">
-        <v>29.92</v>
+        <v>1056.313862392149</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1210.2445873942</v>
+        <v>576.0083476291953</v>
       </c>
       <c r="C10" t="n">
-        <v>1336.246593212636</v>
+        <v>702.0103534476311</v>
       </c>
       <c r="D10" t="n">
-        <v>1386.743548464727</v>
+        <v>815.3294975726312</v>
       </c>
       <c r="E10" t="n">
-        <v>1386.743548464727</v>
+        <v>933.1584017840443</v>
       </c>
       <c r="F10" t="n">
-        <v>1386.743548464727</v>
+        <v>1057.51937437598</v>
       </c>
       <c r="G10" t="n">
-        <v>1386.743548464727</v>
+        <v>1211.108035344832</v>
       </c>
       <c r="H10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="I10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="J10" t="n">
-        <v>1386.743548464727</v>
+        <v>1251.462556240126</v>
       </c>
       <c r="K10" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>218.7737217817557</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>465.3348468790587</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>664.1562397650047</v>
+        <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>836.0471580246821</v>
+        <v>201.8109182596774</v>
       </c>
       <c r="X10" t="n">
-        <v>987.0779490488756</v>
+        <v>352.841709283871</v>
       </c>
       <c r="Y10" t="n">
-        <v>1098.487249727908</v>
+        <v>464.2510099629032</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>607.5035534240029</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C11" t="n">
-        <v>475.7110501482515</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D11" t="n">
-        <v>383.4492766736557</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E11" t="n">
-        <v>297.2237316162127</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F11" t="n">
-        <v>210.4665309010492</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G11" t="n">
         <v>127.0464193797368</v>
@@ -5032,25 +5032,25 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K11" t="n">
-        <v>790.1259849731395</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L11" t="n">
-        <v>1438.575984973139</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M11" t="n">
-        <v>1438.575984973139</v>
+        <v>1632.421694143183</v>
       </c>
       <c r="N11" t="n">
-        <v>1637.361628029778</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O11" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P11" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q11" t="n">
         <v>2620</v>
@@ -5071,13 +5071,13 @@
         <v>1565.051083807838</v>
       </c>
       <c r="W11" t="n">
-        <v>1242.451613120012</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X11" t="n">
-        <v>966.4093570991351</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y11" t="n">
-        <v>772.1493240861994</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="12">
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>180.5214748259267</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C12" t="n">
-        <v>137.9963107395436</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D12" t="n">
         <v>108.7663239741874</v>
@@ -5132,31 +5132,31 @@
         <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2240.946636437805</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2059.873923335154</v>
+        <v>1907.723677356515</v>
       </c>
       <c r="S12" t="n">
-        <v>1925.630174562057</v>
+        <v>1773.479928583418</v>
       </c>
       <c r="T12" t="n">
-        <v>1841.614069044081</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U12" t="n">
-        <v>1759.635861167391</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V12" t="n">
-        <v>1663.160439761815</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W12" t="n">
-        <v>1226.419891368049</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X12" t="n">
-        <v>802.3161141504859</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y12" t="n">
-        <v>398.8904648917643</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="13">
@@ -5190,7 +5190,7 @@
         <v>1163.862419205317</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
@@ -5254,10 +5254,10 @@
         <v>383.4492766736557</v>
       </c>
       <c r="E14" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F14" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G14" t="n">
         <v>127.0464193797368</v>
@@ -5275,10 +5275,10 @@
         <v>1216.127674193434</v>
       </c>
       <c r="L14" t="n">
-        <v>1446.624956504992</v>
+        <v>1864.577674193434</v>
       </c>
       <c r="M14" t="n">
-        <v>1585.241587554805</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="N14" t="n">
         <v>2233.691587554807</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>502.743697048149</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C15" t="n">
         <v>137.9963107395436</v>
@@ -5384,16 +5384,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V15" t="n">
-        <v>1511.010193783177</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W15" t="n">
-        <v>1396.491867611633</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X15" t="n">
-        <v>1294.610312616292</v>
+        <v>972.3880903940691</v>
       </c>
       <c r="Y15" t="n">
-        <v>891.1846633575699</v>
+        <v>568.9624411353475</v>
       </c>
     </row>
     <row r="16">
@@ -5433,25 +5433,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291076</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.839881046618</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O16" t="n">
-        <v>1109.635154952564</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P16" t="n">
-        <v>818.3161660963807</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078979</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755651</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C17" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D17" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E17" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F17" t="n">
         <v>211.1696470591248</v>
@@ -5509,22 +5509,22 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K17" t="n">
-        <v>790.1259849731395</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>1438.575984973139</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M17" t="n">
-        <v>1585.241587554805</v>
+        <v>1206.420004922888</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554807</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O17" t="n">
-        <v>2410.244759641279</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P17" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q17" t="n">
         <v>2620</v>
@@ -5533,25 +5533,25 @@
         <v>2620</v>
       </c>
       <c r="S17" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T17" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U17" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V17" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W17" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X17" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y17" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1372.382356401963</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C18" t="n">
-        <v>1104.66297740621</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D18" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F18" t="n">
         <v>64.01042542894548</v>
@@ -5621,16 +5621,16 @@
         <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y18" t="n">
-        <v>1438.601100489161</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="19">
@@ -5640,22 +5640,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>673.4417775581347</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C19" t="n">
-        <v>719.2537833765705</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D19" t="n">
-        <v>752.3829275015705</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E19" t="n">
-        <v>790.0218317129835</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F19" t="n">
-        <v>834.192804304919</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G19" t="n">
-        <v>908.064555437706</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H19" t="n">
         <v>1003.21633305612</v>
@@ -5670,25 +5670,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L19" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M19" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N19" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O19" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P19" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q19" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R19" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5697,19 +5697,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U19" t="n">
-        <v>329.4820370429934</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V19" t="n">
-        <v>448.1134299289394</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W19" t="n">
-        <v>539.8143481886168</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X19" t="n">
-        <v>610.6551392128104</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y19" t="n">
-        <v>641.8744398918426</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="20">
@@ -5743,16 +5743,16 @@
         <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K20" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L20" t="n">
-        <v>1585.241587554804</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M20" t="n">
-        <v>2233.691587554807</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N20" t="n">
         <v>2233.691587554807</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>502.743697048149</v>
+        <v>1147.188141492594</v>
       </c>
       <c r="C21" t="n">
-        <v>137.9963107395436</v>
+        <v>782.4407551839881</v>
       </c>
       <c r="D21" t="n">
-        <v>108.7663239741874</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E21" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F21" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5861,13 +5861,13 @@
         <v>1736.204408692546</v>
       </c>
       <c r="W21" t="n">
-        <v>1396.491867611633</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X21" t="n">
-        <v>1294.610312616292</v>
+        <v>1294.610312616291</v>
       </c>
       <c r="Y21" t="n">
-        <v>891.1846633575699</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H22" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K22" t="n">
         <v>1597.372803794637</v>
@@ -5910,7 +5910,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N22" t="n">
         <v>1339.839881046618</v>
@@ -5925,7 +5925,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755651</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5934,19 +5934,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V22" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="23">
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>607.5035534240366</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C23" t="n">
-        <v>475.7110501482852</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D23" t="n">
-        <v>383.4492766736894</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E23" t="n">
-        <v>297.2237316162463</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F23" t="n">
-        <v>210.4665309010828</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G23" t="n">
-        <v>126.3433032216949</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H23" t="n">
         <v>52.4</v>
@@ -5980,16 +5980,16 @@
         <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>288.3415875548045</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>936.7915875548044</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L23" t="n">
-        <v>1585.241587554804</v>
+        <v>1438.575984973139</v>
       </c>
       <c r="M23" t="n">
-        <v>2233.691587554807</v>
+        <v>1585.241587554807</v>
       </c>
       <c r="N23" t="n">
         <v>2233.691587554807</v>
@@ -6004,28 +6004,28 @@
         <v>2620</v>
       </c>
       <c r="R23" t="n">
-        <v>2620.000000000034</v>
+        <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2476.335336314626</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2212.479660135832</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.042017309714</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.051083807871</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1242.451613120045</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
-        <v>966.4093570991688</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.149324086233</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="24">
@@ -6035,13 +6035,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1147.188141492594</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C24" t="n">
-        <v>782.4407551839881</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D24" t="n">
-        <v>430.9885461964096</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E24" t="n">
         <v>84.85511465912413</v>
@@ -6101,10 +6101,10 @@
         <v>1621.686082521002</v>
       </c>
       <c r="X24" t="n">
-        <v>1519.804527525661</v>
+        <v>1294.610312616292</v>
       </c>
       <c r="Y24" t="n">
-        <v>1438.601100489161</v>
+        <v>891.1846633575699</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1109.635154952564</v>
       </c>
       <c r="P25" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q25" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6193,55 +6193,55 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>608.2066695820786</v>
+        <v>608.2066695820788</v>
       </c>
       <c r="C26" t="n">
-        <v>476.4141663063272</v>
+        <v>476.4141663063273</v>
       </c>
       <c r="D26" t="n">
-        <v>384.1523928317314</v>
+        <v>384.1523928317316</v>
       </c>
       <c r="E26" t="n">
-        <v>297.9268477742883</v>
+        <v>297.9268477742885</v>
       </c>
       <c r="F26" t="n">
-        <v>211.1696470591248</v>
+        <v>211.169647059125</v>
       </c>
       <c r="G26" t="n">
-        <v>127.0464193797368</v>
+        <v>127.046419379737</v>
       </c>
       <c r="H26" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I26" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J26" t="n">
-        <v>567.6776741934345</v>
+        <v>567.6776741934348</v>
       </c>
       <c r="K26" t="n">
-        <v>753.4744118316256</v>
+        <v>753.4744118316258</v>
       </c>
       <c r="L26" t="n">
-        <v>1401.924411831626</v>
+        <v>1401.924411831628</v>
       </c>
       <c r="M26" t="n">
-        <v>2050.374411831626</v>
+        <v>2050.37441183163</v>
       </c>
       <c r="N26" t="n">
-        <v>2233.691587554807</v>
+        <v>2233.691587554816</v>
       </c>
       <c r="O26" t="n">
-        <v>2410.244759641279</v>
+        <v>2410.244759641288</v>
       </c>
       <c r="P26" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="R26" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="S26" t="n">
         <v>2477.038452472668</v>
@@ -6259,10 +6259,10 @@
         <v>1243.154729278087</v>
       </c>
       <c r="X26" t="n">
-        <v>967.1124732572108</v>
+        <v>967.112473257211</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.852440244275</v>
+        <v>772.8524402442753</v>
       </c>
     </row>
     <row r="27">
@@ -6272,40 +6272,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>180.5214748259267</v>
+        <v>180.5214748259269</v>
       </c>
       <c r="C27" t="n">
-        <v>137.9963107395436</v>
+        <v>137.9963107395438</v>
       </c>
       <c r="D27" t="n">
-        <v>108.7663239741874</v>
+        <v>108.7663239741876</v>
       </c>
       <c r="E27" t="n">
-        <v>84.85511465912413</v>
+        <v>84.8551146591243</v>
       </c>
       <c r="F27" t="n">
-        <v>64.01042542894548</v>
+        <v>64.01042542894565</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964034</v>
       </c>
       <c r="H27" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I27" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J27" t="n">
-        <v>250.191345930016</v>
+        <v>250.1913459300161</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772295</v>
+        <v>565.5796394772298</v>
       </c>
       <c r="L27" t="n">
         <v>1006.615493996958</v>
       </c>
       <c r="M27" t="n">
-        <v>1290.710885739817</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N27" t="n">
         <v>1627.24688421531</v>
@@ -6329,19 +6329,19 @@
         <v>1914.658037974811</v>
       </c>
       <c r="U27" t="n">
-        <v>1832.679830098122</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692546</v>
+        <v>1091.759964248101</v>
       </c>
       <c r="W27" t="n">
-        <v>1396.491867611632</v>
+        <v>977.2416380765571</v>
       </c>
       <c r="X27" t="n">
-        <v>972.3880903940691</v>
+        <v>553.1378608589939</v>
       </c>
       <c r="Y27" t="n">
-        <v>568.9624411353475</v>
+        <v>471.9344338224946</v>
       </c>
     </row>
     <row r="28">
@@ -6351,31 +6351,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581346</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765704</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015704</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129834</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049189</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377058</v>
       </c>
       <c r="H28" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K28" t="n">
         <v>1597.372803794637</v>
@@ -6393,34 +6393,34 @@
         <v>1112.514307960106</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039224</v>
+        <v>821.1953191039227</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154397</v>
+        <v>466.2233328154398</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509823</v>
+        <v>84.56167017509843</v>
       </c>
       <c r="S28" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276573</v>
+        <v>163.0851070276575</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429933</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289391</v>
+        <v>448.1134299289392</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886167</v>
       </c>
       <c r="X28" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128102</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918425</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240116</v>
       </c>
       <c r="C29" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482601</v>
       </c>
       <c r="D29" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736644</v>
       </c>
       <c r="E29" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162213</v>
       </c>
       <c r="F29" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010578</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797368</v>
+        <v>127.046419379737</v>
       </c>
       <c r="H29" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I29" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J29" t="n">
-        <v>141.6759849731395</v>
+        <v>141.6759849731397</v>
       </c>
       <c r="K29" t="n">
-        <v>327.4727226113304</v>
+        <v>790.1259849731417</v>
       </c>
       <c r="L29" t="n">
-        <v>975.9227226113303</v>
+        <v>1020.6232672847</v>
       </c>
       <c r="M29" t="n">
-        <v>1624.372722611331</v>
+        <v>1669.073267284702</v>
       </c>
       <c r="N29" t="n">
-        <v>1637.361628029778</v>
+        <v>2233.691587554816</v>
       </c>
       <c r="O29" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641288</v>
       </c>
       <c r="P29" t="n">
-        <v>2023.670040474971</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="R29" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.335336314592</v>
+        <v>2476.335336314601</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660135798</v>
+        <v>2212.479660135807</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.042017309689</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807846</v>
       </c>
       <c r="W29" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.45161312002</v>
       </c>
       <c r="X29" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991438</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.852440244275</v>
+        <v>772.149324086208</v>
       </c>
     </row>
     <row r="30">
@@ -6509,40 +6509,40 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1372.382356401963</v>
+        <v>824.9659192703714</v>
       </c>
       <c r="C30" t="n">
-        <v>1104.66297740621</v>
+        <v>460.218532961766</v>
       </c>
       <c r="D30" t="n">
-        <v>753.2107684186319</v>
+        <v>108.7663239741876</v>
       </c>
       <c r="E30" t="n">
-        <v>407.0773368813464</v>
+        <v>84.8551146591243</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542894548</v>
+        <v>64.01042542894565</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964035</v>
       </c>
       <c r="H30" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I30" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J30" t="n">
-        <v>250.191345930016</v>
+        <v>250.1913459300161</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772295</v>
+        <v>565.5796394772298</v>
       </c>
       <c r="L30" t="n">
         <v>1006.615493996958</v>
       </c>
       <c r="M30" t="n">
-        <v>1290.710885739817</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N30" t="n">
         <v>1627.24688421531</v>
@@ -6575,10 +6575,10 @@
         <v>1621.686082521002</v>
       </c>
       <c r="X30" t="n">
-        <v>1519.804527525661</v>
+        <v>1294.610312616292</v>
       </c>
       <c r="Y30" t="n">
-        <v>1438.601100489161</v>
+        <v>1213.406885579792</v>
       </c>
     </row>
     <row r="31">
@@ -6588,31 +6588,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581346</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765704</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015704</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129834</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049189</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377058</v>
       </c>
       <c r="H31" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
         <v>1597.372803794637</v>
@@ -6621,43 +6621,43 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M31" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N31" t="n">
-        <v>1339.839881046618</v>
+        <v>1339.839881046619</v>
       </c>
       <c r="O31" t="n">
-        <v>1109.635154952564</v>
+        <v>1109.635154952565</v>
       </c>
       <c r="P31" t="n">
-        <v>818.3161660963807</v>
+        <v>818.3161660963812</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.3441798078979</v>
+        <v>463.3441798078983</v>
       </c>
       <c r="R31" t="n">
-        <v>81.68251716755645</v>
+        <v>81.68251716755691</v>
       </c>
       <c r="S31" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276573</v>
+        <v>163.0851070276575</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429933</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289391</v>
+        <v>448.1134299289392</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886167</v>
       </c>
       <c r="X31" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128102</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918425</v>
       </c>
     </row>
     <row r="32">
@@ -6667,55 +6667,55 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820786</v>
+        <v>608.2066695820788</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063272</v>
+        <v>476.4141663063273</v>
       </c>
       <c r="D32" t="n">
-        <v>384.1523928317314</v>
+        <v>384.1523928317316</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742883</v>
+        <v>297.9268477742885</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591248</v>
+        <v>211.169647059125</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797368</v>
+        <v>127.046419379737</v>
       </c>
       <c r="H32" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I32" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J32" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731397</v>
       </c>
       <c r="K32" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731417</v>
       </c>
       <c r="L32" t="n">
-        <v>1864.577674193434</v>
+        <v>1020.6232672847</v>
       </c>
       <c r="M32" t="n">
-        <v>2233.691587554807</v>
+        <v>1669.073267284702</v>
       </c>
       <c r="N32" t="n">
-        <v>2233.691587554807</v>
+        <v>2233.691587554816</v>
       </c>
       <c r="O32" t="n">
-        <v>2410.244759641279</v>
+        <v>2410.244759641288</v>
       </c>
       <c r="P32" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="R32" t="n">
-        <v>2620</v>
+        <v>2620.000000000009</v>
       </c>
       <c r="S32" t="n">
         <v>2477.038452472668</v>
@@ -6733,10 +6733,10 @@
         <v>1243.154729278087</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572108</v>
+        <v>967.112473257211</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.852440244275</v>
+        <v>772.8524402442753</v>
       </c>
     </row>
     <row r="33">
@@ -6749,37 +6749,37 @@
         <v>1372.382356401963</v>
       </c>
       <c r="C33" t="n">
-        <v>1104.66297740621</v>
+        <v>1104.662977406211</v>
       </c>
       <c r="D33" t="n">
-        <v>753.2107684186319</v>
+        <v>753.2107684186321</v>
       </c>
       <c r="E33" t="n">
-        <v>407.0773368813464</v>
+        <v>407.0773368813466</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542894548</v>
+        <v>64.01042542894565</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964018</v>
+        <v>58.00018335964035</v>
       </c>
       <c r="H33" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="I33" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="J33" t="n">
-        <v>250.191345930016</v>
+        <v>250.1913459300161</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772295</v>
+        <v>565.5796394772298</v>
       </c>
       <c r="L33" t="n">
         <v>1006.615493996958</v>
       </c>
       <c r="M33" t="n">
-        <v>1290.710885739817</v>
+        <v>1290.710885739818</v>
       </c>
       <c r="N33" t="n">
         <v>1627.24688421531</v>
@@ -6825,22 +6825,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581351</v>
+        <v>673.4417775581346</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765708</v>
+        <v>719.2537833765704</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015709</v>
+        <v>752.3829275015704</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129838</v>
+        <v>790.0218317129834</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049194</v>
+        <v>834.1928043049189</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377063</v>
+        <v>908.0645554377058</v>
       </c>
       <c r="H34" t="n">
         <v>1003.21633305612</v>
@@ -6852,10 +6852,10 @@
         <v>1491.077756743015</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L34" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M34" t="n">
         <v>1495.154513298618</v>
@@ -6867,34 +6867,34 @@
         <v>1112.514307960106</v>
       </c>
       <c r="P34" t="n">
-        <v>821.1953191039224</v>
+        <v>821.1953191039227</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154397</v>
+        <v>466.2233328154398</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509823</v>
+        <v>84.56167017509841</v>
       </c>
       <c r="S34" t="n">
-        <v>52.4</v>
+        <v>52.40000000000018</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276573</v>
+        <v>163.0851070276575</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429933</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289391</v>
+        <v>448.1134299289392</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886167</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128107</v>
+        <v>610.6551392128102</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918429</v>
+        <v>641.8744398918425</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>117.1408562629478</v>
+        <v>117.140856262948</v>
       </c>
       <c r="C35" t="n">
-        <v>64.13623177507515</v>
+        <v>64.13623177507532</v>
       </c>
       <c r="D35" t="n">
-        <v>50.66233708835819</v>
+        <v>50.66233708835836</v>
       </c>
       <c r="E35" t="n">
-        <v>43.2246708187939</v>
+        <v>43.22467081879407</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889150919</v>
+        <v>35.25534889150936</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731395</v>
+        <v>119.1959849731397</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113305</v>
+        <v>304.9927226113306</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228883</v>
+        <v>535.4900049228884</v>
       </c>
       <c r="M35" t="n">
-        <v>905.7500049228884</v>
+        <v>905.7500049228885</v>
       </c>
       <c r="N35" t="n">
-        <v>905.7500049228884</v>
+        <v>1109.691587554816</v>
       </c>
       <c r="O35" t="n">
-        <v>1082.303177009361</v>
+        <v>1286.244759641288</v>
       </c>
       <c r="P35" t="n">
-        <v>1292.058417368081</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R35" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="S35" t="n">
-        <v>1434.457487638385</v>
+        <v>1434.457487638386</v>
       </c>
       <c r="T35" t="n">
         <v>1249.38969024747</v>
       </c>
       <c r="U35" t="n">
-        <v>994.7399262092307</v>
+        <v>994.7399262092309</v>
       </c>
       <c r="V35" t="n">
-        <v>759.5368714952672</v>
+        <v>759.5368714952674</v>
       </c>
       <c r="W35" t="n">
-        <v>515.7252795953201</v>
+        <v>515.7252795953203</v>
       </c>
       <c r="X35" t="n">
-        <v>318.4709023623224</v>
+        <v>318.4709023623226</v>
       </c>
       <c r="Y35" t="n">
-        <v>202.9987481372655</v>
+        <v>202.9987481372656</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>221.786275057013</v>
+        <v>458.0444483210439</v>
       </c>
       <c r="C36" t="n">
-        <v>221.786275057013</v>
+        <v>458.0444483210439</v>
       </c>
       <c r="D36" t="n">
-        <v>221.786275057013</v>
+        <v>221.7862750570132</v>
       </c>
       <c r="E36" t="n">
-        <v>221.786275057013</v>
+        <v>221.7862750570132</v>
       </c>
       <c r="F36" t="n">
-        <v>221.786275057013</v>
+        <v>221.7862750570132</v>
       </c>
       <c r="G36" t="n">
-        <v>221.786275057013</v>
+        <v>221.7862750570132</v>
       </c>
       <c r="H36" t="n">
-        <v>221.786275057013</v>
+        <v>221.7862750570132</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J36" t="n">
-        <v>227.711345930016</v>
+        <v>227.7113459300161</v>
       </c>
       <c r="K36" t="n">
-        <v>543.0996394772296</v>
+        <v>543.0996394772297</v>
       </c>
       <c r="L36" t="n">
-        <v>599.927050901758</v>
+        <v>599.9270509017581</v>
       </c>
       <c r="M36" t="n">
-        <v>884.0224426446173</v>
+        <v>851.5752611841849</v>
       </c>
       <c r="N36" t="n">
-        <v>1188.111259659669</v>
+        <v>1188.111259659678</v>
       </c>
       <c r="O36" t="n">
-        <v>1234.237999492757</v>
+        <v>1234.237999492766</v>
       </c>
       <c r="P36" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.95603106927</v>
+        <v>1422.956031069278</v>
       </c>
       <c r="R36" t="n">
-        <v>1320.671196754497</v>
+        <v>1320.671196754506</v>
       </c>
       <c r="S36" t="n">
-        <v>1265.215326769279</v>
+        <v>1265.215326769288</v>
       </c>
       <c r="T36" t="n">
-        <v>1259.987100039182</v>
+        <v>1259.98710003919</v>
       </c>
       <c r="U36" t="n">
-        <v>1256.796770950371</v>
+        <v>1256.796770950379</v>
       </c>
       <c r="V36" t="n">
-        <v>1239.109228332674</v>
+        <v>1239.109228332682</v>
       </c>
       <c r="W36" t="n">
-        <v>977.3418306125686</v>
+        <v>861.3314505549044</v>
       </c>
       <c r="X36" t="n">
-        <v>599.5640528347908</v>
+        <v>838.2377743474423</v>
       </c>
       <c r="Y36" t="n">
-        <v>221.786275057013</v>
+        <v>835.8222260988217</v>
       </c>
     </row>
     <row r="37">
@@ -7062,31 +7062,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.92</v>
+        <v>564.1283476291956</v>
       </c>
       <c r="C37" t="n">
-        <v>29.92</v>
+        <v>687.1603534476313</v>
       </c>
       <c r="D37" t="n">
-        <v>140.2691441250001</v>
+        <v>797.5094975726314</v>
       </c>
       <c r="E37" t="n">
-        <v>255.1280483364131</v>
+        <v>797.5094975726314</v>
       </c>
       <c r="F37" t="n">
-        <v>310.4153075443083</v>
+        <v>918.9004701645669</v>
       </c>
       <c r="G37" t="n">
-        <v>461.5070586770952</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="H37" t="n">
-        <v>633.8788362955091</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="I37" t="n">
-        <v>871.7449224447068</v>
+        <v>1055.259969496329</v>
       </c>
       <c r="J37" t="n">
-        <v>883.150259982404</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="K37" t="n">
         <v>1066.665307034026</v>
@@ -7104,34 +7104,34 @@
         <v>821.5090014213715</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530666</v>
+        <v>608.9778913530668</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524626</v>
+        <v>332.7937838524628</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="T37" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="U37" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="V37" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="W37" t="n">
-        <v>29.92</v>
+        <v>198.8409182596776</v>
       </c>
       <c r="X37" t="n">
-        <v>29.92</v>
+        <v>346.9017092838711</v>
       </c>
       <c r="Y37" t="n">
-        <v>29.92</v>
+        <v>455.3410099629034</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.806583727033</v>
+        <v>113.8065837270417</v>
       </c>
       <c r="C38" t="n">
-        <v>60.80195923916038</v>
+        <v>60.80195923916902</v>
       </c>
       <c r="D38" t="n">
-        <v>47.32806455244342</v>
+        <v>47.32806455245206</v>
       </c>
       <c r="E38" t="n">
-        <v>39.89039828287913</v>
+        <v>39.89039828288777</v>
       </c>
       <c r="F38" t="n">
-        <v>31.92107635559443</v>
+        <v>31.92107635560307</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1959849731395</v>
+        <v>119.1959849731397</v>
       </c>
       <c r="K38" t="n">
-        <v>304.9927226113305</v>
+        <v>304.9927226113306</v>
       </c>
       <c r="L38" t="n">
-        <v>535.4900049228883</v>
+        <v>535.4900049228884</v>
       </c>
       <c r="M38" t="n">
-        <v>535.4900049228884</v>
+        <v>739.4315875548157</v>
       </c>
       <c r="N38" t="n">
-        <v>755.48</v>
+        <v>1109.691587554816</v>
       </c>
       <c r="O38" t="n">
-        <v>1125.74</v>
+        <v>1286.244759641288</v>
       </c>
       <c r="P38" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R38" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.123215102471</v>
+        <v>1431.123215102479</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417711555</v>
+        <v>1246.055417711564</v>
       </c>
       <c r="U38" t="n">
-        <v>991.405653673316</v>
+        <v>991.4056536733245</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989593525</v>
+        <v>756.202598959361</v>
       </c>
       <c r="W38" t="n">
-        <v>512.3910070594054</v>
+        <v>512.3910070594141</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298264077</v>
+        <v>315.1366298264163</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756013507</v>
+        <v>199.6644756013594</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>586.5336613656184</v>
+        <v>1092.253026833469</v>
       </c>
       <c r="C39" t="n">
-        <v>221.786275057013</v>
+        <v>727.5056405248641</v>
       </c>
       <c r="D39" t="n">
-        <v>221.786275057013</v>
+        <v>376.0534315372857</v>
       </c>
       <c r="E39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="F39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="G39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="H39" t="n">
-        <v>221.786275057013</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J39" t="n">
-        <v>227.711345930016</v>
+        <v>227.7113459300161</v>
       </c>
       <c r="K39" t="n">
-        <v>543.0996394772296</v>
+        <v>543.0996394772297</v>
       </c>
       <c r="L39" t="n">
-        <v>599.927050901758</v>
+        <v>599.9270509017581</v>
       </c>
       <c r="M39" t="n">
         <v>884.0224426446173</v>
       </c>
       <c r="N39" t="n">
-        <v>884.0224426446173</v>
+        <v>1188.111259659678</v>
       </c>
       <c r="O39" t="n">
-        <v>1234.237999492757</v>
+        <v>1234.237999492766</v>
       </c>
       <c r="P39" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q39" t="n">
-        <v>1422.95603106927</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R39" t="n">
-        <v>1045.178253291492</v>
+        <v>1393.715165685236</v>
       </c>
       <c r="S39" t="n">
-        <v>989.7223833062737</v>
+        <v>1338.259295700018</v>
       </c>
       <c r="T39" t="n">
-        <v>984.4941565761759</v>
+        <v>1333.03106896992</v>
       </c>
       <c r="U39" t="n">
-        <v>981.3038274873652</v>
+        <v>1329.84073988111</v>
       </c>
       <c r="V39" t="n">
-        <v>963.6162848696681</v>
+        <v>1312.153197263413</v>
       </c>
       <c r="W39" t="n">
-        <v>927.885837486003</v>
+        <v>1276.422749879747</v>
       </c>
       <c r="X39" t="n">
-        <v>904.7921612785408</v>
+        <v>1094.66857508209</v>
       </c>
       <c r="Y39" t="n">
-        <v>902.3766130299202</v>
+        <v>1092.253026833469</v>
       </c>
     </row>
     <row r="40">
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>551.4432280029315</v>
+        <v>419.8140573923044</v>
       </c>
       <c r="C40" t="n">
-        <v>551.4432280029315</v>
+        <v>419.8140573923044</v>
       </c>
       <c r="D40" t="n">
-        <v>551.4432280029315</v>
+        <v>530.1632015173045</v>
       </c>
       <c r="E40" t="n">
-        <v>666.3021322143445</v>
+        <v>645.0221057287175</v>
       </c>
       <c r="F40" t="n">
-        <v>666.3021322143445</v>
+        <v>645.0221057287175</v>
       </c>
       <c r="G40" t="n">
-        <v>817.3938833471315</v>
+        <v>645.0221057287175</v>
       </c>
       <c r="H40" t="n">
         <v>817.3938833471315</v>
@@ -7341,34 +7341,34 @@
         <v>821.5090014213715</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530666</v>
+        <v>608.9778913530668</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524626</v>
+        <v>332.7937838524628</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="T40" t="n">
-        <v>165.2956713979297</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="U40" t="n">
-        <v>165.2956713979297</v>
+        <v>115.1753268400663</v>
       </c>
       <c r="V40" t="n">
-        <v>165.2956713979297</v>
+        <v>311.0267197260123</v>
       </c>
       <c r="W40" t="n">
-        <v>334.2165896576071</v>
+        <v>311.0267197260123</v>
       </c>
       <c r="X40" t="n">
-        <v>334.2165896576071</v>
+        <v>311.0267197260123</v>
       </c>
       <c r="Y40" t="n">
-        <v>442.6558903366393</v>
+        <v>311.0267197260123</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92</v>
+        <v>612.3367715680868</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92</v>
+        <v>454.281642029709</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92</v>
+        <v>335.757242292487</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92</v>
+        <v>223.2690709724177</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92</v>
+        <v>110.2492439946279</v>
       </c>
       <c r="G41" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731395</v>
+        <v>400.1800000000002</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113305</v>
+        <v>585.976737638191</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228883</v>
+        <v>816.4740199497488</v>
       </c>
       <c r="M41" t="n">
-        <v>535.4900049228884</v>
+        <v>1109.691587554816</v>
       </c>
       <c r="N41" t="n">
-        <v>755.48</v>
+        <v>1109.691587554816</v>
       </c>
       <c r="O41" t="n">
-        <v>1125.74</v>
+        <v>1286.244759641288</v>
       </c>
       <c r="P41" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R41" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="S41" t="n">
-        <v>1330.90555076412</v>
+        <v>1326.072710051974</v>
       </c>
       <c r="T41" t="n">
-        <v>1040.787248322699</v>
+        <v>1326.072710051974</v>
       </c>
       <c r="U41" t="n">
-        <v>681.0869792339549</v>
+        <v>1326.072710051974</v>
       </c>
       <c r="V41" t="n">
-        <v>681.0869792339549</v>
+        <v>1326.072710051974</v>
       </c>
       <c r="W41" t="n">
-        <v>332.2248822835028</v>
+        <v>1326.072710051974</v>
       </c>
       <c r="X41" t="n">
-        <v>29.92</v>
+        <v>1023.767827768472</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92</v>
+        <v>803.2451684929096</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016843</v>
+        <v>318.0281146697992</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526749</v>
+        <v>249.2403243207898</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246924</v>
+        <v>193.7477112928073</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470029</v>
+        <v>143.5738757151178</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419802</v>
+        <v>96.46656022231291</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226643</v>
+        <v>64.19369189038133</v>
       </c>
       <c r="H42" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J42" t="n">
-        <v>227.711345930016</v>
+        <v>227.7113459300161</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772296</v>
+        <v>543.0996394772297</v>
       </c>
       <c r="L42" t="n">
-        <v>599.927050901758</v>
+        <v>913.3596394772297</v>
       </c>
       <c r="M42" t="n">
-        <v>884.0224426446173</v>
+        <v>1080.93720421491</v>
       </c>
       <c r="N42" t="n">
-        <v>884.0224426446173</v>
+        <v>1080.93720421491</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492757</v>
+        <v>1451.19720421491</v>
       </c>
       <c r="P42" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q42" t="n">
-        <v>1493.589117731894</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R42" t="n">
-        <v>1286.253778366616</v>
+        <v>1288.664660634731</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330893</v>
+        <v>1128.158285599008</v>
       </c>
       <c r="T42" t="n">
-        <v>1015.46867155029</v>
+        <v>1017.879553818405</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109744</v>
+        <v>909.6387196790894</v>
       </c>
       <c r="V42" t="n">
-        <v>784.4897897427722</v>
+        <v>786.9006720108872</v>
       </c>
       <c r="W42" t="n">
-        <v>643.708837308602</v>
+        <v>646.119719576717</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506348</v>
+        <v>517.9755383187497</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515092</v>
+        <v>410.5094850196241</v>
       </c>
     </row>
     <row r="43">
@@ -7536,28 +7536,28 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581344</v>
+        <v>470.7817775581345</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765702</v>
+        <v>490.8537833765703</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015703</v>
+        <v>498.2429275015704</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129833</v>
+        <v>510.1418317129834</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049188</v>
+        <v>528.5728043049189</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377057</v>
+        <v>576.7045554377058</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561196</v>
+        <v>646.1163330561199</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053173</v>
+        <v>781.0224192053175</v>
       </c>
       <c r="J43" t="n">
         <v>1082.497756743015</v>
@@ -7572,40 +7572,40 @@
         <v>1163.052803794637</v>
       </c>
       <c r="N43" t="n">
-        <v>984.3546982875537</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="O43" t="n">
-        <v>727.8873459308736</v>
+        <v>906.5854514379571</v>
       </c>
       <c r="P43" t="n">
-        <v>410.3057308120637</v>
+        <v>589.0038363191472</v>
       </c>
       <c r="Q43" t="n">
-        <v>32.52795303428587</v>
+        <v>211.2260585413694</v>
       </c>
       <c r="R43" t="n">
-        <v>29.92</v>
+        <v>88.34429643772467</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276573</v>
+        <v>114.8651070276575</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370429931</v>
+        <v>255.5220370429933</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289391</v>
+        <v>348.4134299289393</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886165</v>
+        <v>414.3743481886166</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128101</v>
+        <v>459.4751392128102</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918423</v>
+        <v>464.9544398918424</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>401.9040021585306</v>
+        <v>144.8791919128408</v>
       </c>
       <c r="C44" t="n">
-        <v>243.8488726201529</v>
+        <v>144.8791919128408</v>
       </c>
       <c r="D44" t="n">
-        <v>243.8488726201529</v>
+        <v>144.8791919128408</v>
       </c>
       <c r="E44" t="n">
-        <v>243.8488726201529</v>
+        <v>144.8791919128408</v>
       </c>
       <c r="F44" t="n">
-        <v>130.8290456423631</v>
+        <v>31.85936493505108</v>
       </c>
       <c r="G44" t="n">
-        <v>130.8290456423631</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="H44" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I44" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731395</v>
+        <v>119.1959849731397</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113305</v>
+        <v>304.9927226113306</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228883</v>
+        <v>535.4900049228884</v>
       </c>
       <c r="M44" t="n">
-        <v>905.7500049228884</v>
+        <v>535.4900049228885</v>
       </c>
       <c r="N44" t="n">
-        <v>915.9847596412797</v>
+        <v>739.4315875548157</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.24475964128</v>
+        <v>915.9847596412883</v>
       </c>
       <c r="P44" t="n">
-        <v>1496</v>
+        <v>1125.740000000009</v>
       </c>
       <c r="Q44" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R44" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="S44" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="T44" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="U44" t="n">
-        <v>1393.324541156954</v>
+        <v>1136.299730911264</v>
       </c>
       <c r="V44" t="n">
-        <v>1053.070981392485</v>
+        <v>796.0461711467957</v>
       </c>
       <c r="W44" t="n">
-        <v>704.2088844420334</v>
+        <v>447.1840741963436</v>
       </c>
       <c r="X44" t="n">
-        <v>401.9040021585306</v>
+        <v>144.8791919128408</v>
       </c>
       <c r="Y44" t="n">
-        <v>401.9040021585306</v>
+        <v>144.8791919128408</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.6172324016843</v>
+        <v>318.0281146697992</v>
       </c>
       <c r="C45" t="n">
-        <v>246.8294420526749</v>
+        <v>249.2403243207898</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290246924</v>
+        <v>193.7477112928073</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470029</v>
+        <v>143.5738757151178</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795419802</v>
+        <v>96.46656022231291</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962226644</v>
+        <v>64.19369189038133</v>
       </c>
       <c r="H45" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="I45" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="J45" t="n">
-        <v>227.711345930016</v>
+        <v>227.7113459300161</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772296</v>
+        <v>543.0996394772297</v>
       </c>
       <c r="L45" t="n">
-        <v>904.0158679168098</v>
+        <v>904.0158679168185</v>
       </c>
       <c r="M45" t="n">
-        <v>1188.111259659669</v>
+        <v>1188.111259659678</v>
       </c>
       <c r="N45" t="n">
-        <v>1188.111259659669</v>
+        <v>1188.111259659678</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492757</v>
+        <v>1234.237999492766</v>
       </c>
       <c r="P45" t="n">
-        <v>1496</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731894</v>
+        <v>1496.000000000009</v>
       </c>
       <c r="R45" t="n">
-        <v>1286.253778366616</v>
+        <v>1288.664660634731</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330893</v>
+        <v>1128.158285599008</v>
       </c>
       <c r="T45" t="n">
-        <v>1015.46867155029</v>
+        <v>1017.879553818405</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109744</v>
+        <v>909.6387196790894</v>
       </c>
       <c r="V45" t="n">
-        <v>784.4897897427722</v>
+        <v>786.9006720108872</v>
       </c>
       <c r="W45" t="n">
-        <v>643.708837308602</v>
+        <v>646.119719576717</v>
       </c>
       <c r="X45" t="n">
-        <v>515.5646560506348</v>
+        <v>517.9755383187497</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515092</v>
+        <v>410.5094850196241</v>
       </c>
     </row>
     <row r="46">
@@ -7773,28 +7773,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.7817775581344</v>
+        <v>470.7817775581345</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765702</v>
+        <v>490.8537833765703</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015703</v>
+        <v>498.2429275015704</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129833</v>
+        <v>510.1418317129834</v>
       </c>
       <c r="F46" t="n">
-        <v>528.5728043049188</v>
+        <v>528.5728043049189</v>
       </c>
       <c r="G46" t="n">
-        <v>576.7045554377057</v>
+        <v>576.7045554377058</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561196</v>
+        <v>646.1163330561199</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053173</v>
+        <v>781.0224192053175</v>
       </c>
       <c r="J46" t="n">
         <v>1082.497756743015</v>
@@ -7806,43 +7806,43 @@
         <v>1163.052803794637</v>
       </c>
       <c r="M46" t="n">
-        <v>1160.444850760351</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="N46" t="n">
-        <v>981.7467452532678</v>
+        <v>984.3546982875536</v>
       </c>
       <c r="O46" t="n">
-        <v>725.2793928965878</v>
+        <v>727.8873459308734</v>
       </c>
       <c r="P46" t="n">
-        <v>407.6977777777778</v>
+        <v>410.3057308120635</v>
       </c>
       <c r="Q46" t="n">
-        <v>29.92</v>
+        <v>32.52795303428564</v>
       </c>
       <c r="R46" t="n">
-        <v>29.92</v>
+        <v>32.52795303428564</v>
       </c>
       <c r="S46" t="n">
-        <v>29.92</v>
+        <v>29.92000000000017</v>
       </c>
       <c r="T46" t="n">
-        <v>114.8651070276573</v>
+        <v>114.8651070276575</v>
       </c>
       <c r="U46" t="n">
-        <v>255.5220370429931</v>
+        <v>255.5220370429933</v>
       </c>
       <c r="V46" t="n">
-        <v>348.4134299289391</v>
+        <v>348.4134299289393</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886165</v>
+        <v>414.3743481886166</v>
       </c>
       <c r="X46" t="n">
-        <v>459.4751392128101</v>
+        <v>459.4751392128102</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918423</v>
+        <v>464.9544398918424</v>
       </c>
     </row>
   </sheetData>
@@ -7964,13 +7964,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
@@ -7982,10 +7982,10 @@
         <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q2" t="n">
-        <v>311.8831458198699</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,7 +8201,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -8216,7 +8216,7 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -8438,7 +8438,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -8453,7 +8453,7 @@
         <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8675,19 +8675,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N11" t="n">
-        <v>414.7873509852764</v>
+        <v>821.3370988185948</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,13 +8918,13 @@
         <v>467.3265276381908</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M14" t="n">
-        <v>425.2156553257482</v>
+        <v>658.0411930141927</v>
       </c>
       <c r="N14" t="n">
-        <v>868.9937721401893</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9152,16 +9152,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>433.3459296003468</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N17" t="n">
-        <v>868.9937721401893</v>
+        <v>649.2883409350248</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,19 +9386,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L20" t="n">
-        <v>140.0167990402144</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855363</v>
+        <v>433.3459296003492</v>
       </c>
       <c r="N20" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>148.1470733148132</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>467.326527638191</v>
       </c>
       <c r="L23" t="n">
-        <v>422.1744623115578</v>
+        <v>422.1744623115576</v>
       </c>
       <c r="M23" t="n">
-        <v>940.1988562855358</v>
+        <v>433.3459296003492</v>
       </c>
       <c r="N23" t="n">
-        <v>213.993772140187</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9866,13 +9866,13 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>422.1744623115578</v>
+        <v>422.1744623115599</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855336</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N26" t="n">
-        <v>399.1626365070367</v>
+        <v>399.1626365070413</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>467.3265276381931</v>
       </c>
       <c r="L29" t="n">
-        <v>422.1744623115577</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>940.198856285534</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N29" t="n">
-        <v>227.1138786234666</v>
+        <v>784.315307766565</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10334,19 +10334,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>467.3265276381908</v>
+        <v>467.3265276381931</v>
       </c>
       <c r="L32" t="n">
-        <v>422.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>658.0411930141927</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N32" t="n">
-        <v>213.993772140187</v>
+        <v>784.315307766565</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10583,7 +10583,7 @@
         <v>659.1988562855333</v>
       </c>
       <c r="N35" t="n">
-        <v>213.993772140187</v>
+        <v>419.9953707582953</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>219.5001774179469</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10659,10 +10659,10 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>471.6948204301074</v>
+        <v>438.9198896619939</v>
       </c>
       <c r="N36" t="n">
-        <v>452.633596403228</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -10817,16 +10817,16 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>285.1988562855334</v>
+        <v>491.2004549036417</v>
       </c>
       <c r="N38" t="n">
-        <v>436.2058883796937</v>
+        <v>587.993772140187</v>
       </c>
       <c r="O38" t="n">
-        <v>195.6634625389165</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>162.1260198396764</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>13.49857879984722</v>
@@ -10899,10 +10899,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N39" t="n">
-        <v>145.473175175903</v>
+        <v>452.6335964032368</v>
       </c>
       <c r="O39" t="n">
-        <v>307.1604212273249</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>219.1507118405495</v>
@@ -11045,7 +11045,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>283.8222374008692</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -11054,16 +11054,16 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>285.1988562855334</v>
+        <v>581.3782175027727</v>
       </c>
       <c r="N41" t="n">
-        <v>436.2058883796937</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O41" t="n">
-        <v>195.6634625389165</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>162.1260198396764</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>13.49857879984722</v>
@@ -11130,19 +11130,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>316.5985743186583</v>
       </c>
       <c r="M42" t="n">
-        <v>471.6948204301074</v>
+        <v>354.0000456774014</v>
       </c>
       <c r="N42" t="n">
         <v>145.473175175903</v>
       </c>
       <c r="O42" t="n">
-        <v>307.1604212273249</v>
+        <v>327.4073335019309</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11291,19 +11291,19 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>659.1988562855333</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>224.3319082193701</v>
+        <v>419.9953707582953</v>
       </c>
       <c r="O44" t="n">
-        <v>195.6634625389165</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.49857879984722</v>
+        <v>387.4985787998472</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11367,7 +11367,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L45" t="n">
-        <v>307.1604212273252</v>
+        <v>307.1604212273338</v>
       </c>
       <c r="M45" t="n">
         <v>471.6948204301074</v>
@@ -22512,7 +22512,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.526512829121202e-13</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.743938327081196e-12</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23238,7 +23238,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23286,7 +23286,7 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>2.850361477466338</v>
+        <v>2.850361477466563</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -23469,13 +23469,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23648,7 +23648,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.850361477466322</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.850361477466352</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696084996494875</v>
+        <v>0.6960849964948983</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.850361477466322</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24189,7 +24189,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6960849964615505</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -24240,7 +24240,7 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
     </row>
     <row r="24">
@@ -24371,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.850361477466265</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6960849964951876</v>
+        <v>0.6960849964866611</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466563</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.6960849964865281</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24702,7 +24702,7 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>0.6960849964950739</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -24854,7 +24854,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.85036147746635</v>
+        <v>2.850361477466077</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6960849964951876</v>
+        <v>0.6960849964866327</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25070,10 +25070,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>2.850361477465662</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>2.850361477466294</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>3.300929810555573</v>
+        <v>3.300929810547245</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25371,7 +25371,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>3.300929810555617</v>
+        <v>3.300929810547209</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>111.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>109.2819954025941</v>
+        <v>29.75604384791262</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593946</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,25 +25644,25 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4.784512305032536</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
         <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -25781,13 +25781,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712345</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
         <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -25796,13 +25796,13 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266425597968</v>
+        <v>3.422266425597996</v>
       </c>
       <c r="R43" t="n">
-        <v>401.2631725099949</v>
+        <v>282.1921015313297</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334727</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25833,7 +25833,7 @@
         <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>117.3391557398498</v>
@@ -25845,10 +25845,10 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>107.3620241168937</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25887,7 +25887,7 @@
         <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
-        <v>254.4545621432415</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -26021,7 +26021,7 @@
         <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
-        <v>121.3090657674594</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -26039,7 +26039,7 @@
         <v>403.845046013938</v>
       </c>
       <c r="S46" t="n">
-        <v>57.84005347334724</v>
+        <v>55.25817996940462</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8406951.394927315</v>
+        <v>8406951.394927314</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9445835.304142728</v>
+        <v>9445835.30414273</v>
       </c>
     </row>
     <row r="11">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13564350.59146539</v>
+        <v>13564350.5914654</v>
       </c>
     </row>
     <row r="15">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1164923.76230765</v>
+        <v>1164923.762307649</v>
       </c>
       <c r="C2" t="n">
         <v>1164923.76230765</v>
@@ -26287,16 +26287,16 @@
         <v>1164809.231544558</v>
       </c>
       <c r="H2" t="n">
+        <v>1164809.231544557</v>
+      </c>
+      <c r="I2" t="n">
         <v>1164809.231544559</v>
       </c>
-      <c r="I2" t="n">
-        <v>1164809.231544561</v>
-      </c>
       <c r="J2" t="n">
-        <v>1164809.231544557</v>
+        <v>1164809.231544559</v>
       </c>
       <c r="K2" t="n">
-        <v>1164809.231544557</v>
+        <v>1164809.231544558</v>
       </c>
       <c r="L2" t="n">
         <v>1164809.231544557</v>
@@ -26305,10 +26305,10 @@
         <v>1164680.714845699</v>
       </c>
       <c r="N2" t="n">
-        <v>1164680.714845699</v>
+        <v>1164680.7148457</v>
       </c>
       <c r="O2" t="n">
-        <v>1044045.023600558</v>
+        <v>1044045.023600559</v>
       </c>
       <c r="P2" t="n">
         <v>1044045.023600558</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386848</v>
+        <v>386848.0000000008</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687437</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689994</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285019</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045217</v>
+        <v>499902.9383787897</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265499</v>
+        <v>498222.592100818</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963754</v>
+        <v>496539.8583706433</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842147</v>
+        <v>522371.0444804643</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731494</v>
+        <v>520403.9137693991</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155932</v>
+        <v>447670.9673118428</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523478</v>
+        <v>446003.2126485974</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.611</v>
+        <v>74642.61100000014</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.611</v>
+        <v>74642.61100000014</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.611</v>
+        <v>74642.61100000014</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.193</v>
+        <v>64115.19300000013</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.193</v>
+        <v>64115.19300000013</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000001</v>
+        <v>55372.01700000014</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01700000001</v>
+        <v>55372.01700000014</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>272816.1860975316</v>
+        <v>273015.5007527458</v>
       </c>
       <c r="C6" t="n">
-        <v>505923.1082850198</v>
+        <v>506122.422940235</v>
       </c>
       <c r="D6" t="n">
-        <v>507934.7557008442</v>
+        <v>508134.0703560591</v>
       </c>
       <c r="E6" t="n">
-        <v>-30783.99692402346</v>
+        <v>-30589.83849829153</v>
       </c>
       <c r="F6" t="n">
-        <v>583371.6685758147</v>
+        <v>583565.8270015469</v>
       </c>
       <c r="G6" t="n">
-        <v>585042.6367714349</v>
+        <v>585236.7951971673</v>
       </c>
       <c r="H6" t="n">
-        <v>586715.9241755593</v>
+        <v>586910.0826012897</v>
       </c>
       <c r="I6" t="n">
-        <v>588391.5475160585</v>
+        <v>588585.7059417904</v>
       </c>
       <c r="J6" t="n">
-        <v>203221.5237400355</v>
+        <v>203415.6821657686</v>
       </c>
       <c r="K6" t="n">
-        <v>591749.8700180072</v>
+        <v>591944.0284437396</v>
       </c>
       <c r="L6" t="n">
-        <v>593432.6037481816</v>
+        <v>593626.7621739138</v>
       </c>
       <c r="M6" t="n">
-        <v>515675.0602614839</v>
+        <v>515794.4773652343</v>
       </c>
       <c r="N6" t="n">
-        <v>580042.1909725494</v>
+        <v>580161.6080763008</v>
       </c>
       <c r="O6" t="n">
-        <v>368882.6221849645</v>
+        <v>369002.0392887157</v>
       </c>
       <c r="P6" t="n">
-        <v>542550.3768482101</v>
+        <v>542669.7939519607</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="K4" t="n">
-        <v>655</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="L4" t="n">
-        <v>655</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="M4" t="n">
-        <v>374</v>
+        <v>374.0000000000022</v>
       </c>
       <c r="N4" t="n">
-        <v>374</v>
+        <v>374.0000000000022</v>
       </c>
       <c r="O4" t="n">
-        <v>374</v>
+        <v>374.0000000000022</v>
       </c>
       <c r="P4" t="n">
-        <v>374</v>
+        <v>374.0000000000022</v>
       </c>
     </row>
   </sheetData>
@@ -26999,7 +26999,7 @@
         <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27008,7 +27008,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27079,7 +27079,7 @@
         <v>374</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>398.2013121321726</v>
+        <v>398.2013121321716</v>
       </c>
       <c r="G2" t="n">
         <v>400</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>26.1959257979226</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>46.09260856694289</v>
+        <v>77.22458554710784</v>
       </c>
     </row>
     <row r="4">
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>272.7252466480447</v>
@@ -27606,16 +27606,16 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>395.504473841919</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>23.06710116008236</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
@@ -27654,13 +27654,13 @@
         <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27685,7 +27685,7 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27761,16 +27761,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>203.2576378635061</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27797,10 +27797,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>287.049229829184</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27834,10 +27834,10 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>343.8791148384516</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014815</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,16 +27879,16 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
-        <v>269.8873298096613</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
         <v>226.3728098387097</v>
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>159.6519859716246</v>
+        <v>380.5228000092467</v>
       </c>
       <c r="S9" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
         <v>400</v>
@@ -28046,10 +28046,10 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>275.7414117925084</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28071,19 +28071,19 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>336.5432435627184</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>267.8979241578016</v>
       </c>
       <c r="I10" t="n">
         <v>171.1020457840527</v>
@@ -28092,10 +28092,10 @@
         <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,13 +28119,13 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>400</v>
+        <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168.3712564811474</v>
+        <v>319</v>
       </c>
       <c r="C12" t="n">
         <v>319</v>
       </c>
       <c r="D12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>319</v>
@@ -28268,10 +28268,10 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>319</v>
+        <v>96.05772723972416</v>
       </c>
       <c r="S12" t="n">
         <v>319</v>
@@ -28280,19 +28280,19 @@
         <v>319</v>
       </c>
       <c r="U12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>319</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13">
@@ -28323,7 +28323,7 @@
         <v>319</v>
       </c>
       <c r="I13" t="n">
-        <v>319.0000000000001</v>
+        <v>319</v>
       </c>
       <c r="J13" t="n">
         <v>319</v>
@@ -28463,7 +28463,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D15" t="n">
         <v>319</v>
@@ -28520,13 +28520,13 @@
         <v>319</v>
       </c>
       <c r="V15" t="n">
-        <v>96.05772723972467</v>
+        <v>319</v>
       </c>
       <c r="W15" t="n">
-        <v>319</v>
+        <v>96.0577272397241</v>
       </c>
       <c r="X15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
@@ -28700,16 +28700,16 @@
         <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>96.05772723972427</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>319</v>
@@ -28757,16 +28757,16 @@
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28833,7 +28833,7 @@
         <v>319</v>
       </c>
       <c r="U19" t="n">
-        <v>319.0000000000003</v>
+        <v>319</v>
       </c>
       <c r="V19" t="n">
         <v>319</v>
@@ -28934,19 +28934,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>319</v>
       </c>
       <c r="F21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -28997,13 +28997,13 @@
         <v>319</v>
       </c>
       <c r="W21" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="X21" t="n">
-        <v>319</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22">
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>158.2009556122474</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S23" t="n">
         <v>319</v>
@@ -29171,16 +29171,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>96.0577272397245</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F24" t="n">
         <v>319</v>
@@ -29237,10 +29237,10 @@
         <v>319</v>
       </c>
       <c r="X24" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="Y24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -29408,7 +29408,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>96.05772723972461</v>
       </c>
       <c r="C27" t="n">
         <v>319</v>
@@ -29465,19 +29465,19 @@
         <v>319</v>
       </c>
       <c r="U27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>96.0577272397241</v>
+        <v>319</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28">
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>96.05772723972427</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29711,7 +29711,7 @@
         <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="Y30" t="n">
         <v>319</v>
@@ -29885,7 +29885,7 @@
         <v>319</v>
       </c>
       <c r="C33" t="n">
-        <v>96.05772723972427</v>
+        <v>96.0577272397245</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -30027,7 +30027,7 @@
         <v>319</v>
       </c>
       <c r="X34" t="n">
-        <v>319.0000000000007</v>
+        <v>319</v>
       </c>
       <c r="Y34" t="n">
         <v>319</v>
@@ -30119,13 +30119,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632658</v>
       </c>
       <c r="C36" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>114.0420953663123</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30182,13 +30182,13 @@
         <v>397</v>
       </c>
       <c r="W36" t="n">
-        <v>173.2234191669245</v>
+        <v>58.37314290982854</v>
       </c>
       <c r="X36" t="n">
-        <v>45.86273944538755</v>
+        <v>397</v>
       </c>
       <c r="Y36" t="n">
-        <v>25.39139276613435</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37">
@@ -30198,34 +30198,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>287.1138003370787</v>
+        <v>397</v>
       </c>
       <c r="C37" t="n">
-        <v>272.7252466480447</v>
+        <v>397</v>
       </c>
       <c r="D37" t="n">
         <v>397</v>
       </c>
       <c r="E37" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F37" t="n">
         <v>397</v>
       </c>
-      <c r="F37" t="n">
-        <v>330.2285723393533</v>
-      </c>
       <c r="G37" t="n">
-        <v>397</v>
+        <v>382.1189375747226</v>
       </c>
       <c r="H37" t="n">
-        <v>397</v>
+        <v>222.8870933147334</v>
       </c>
       <c r="I37" t="n">
-        <v>397</v>
+        <v>156.7312261119215</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>397</v>
+        <v>211.6312656044217</v>
       </c>
       <c r="L37" t="n">
         <v>325.1555297971234</v>
@@ -30261,13 +30261,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>226.3728098387097</v>
+        <v>397</v>
       </c>
       <c r="X37" t="n">
-        <v>247.4436454301076</v>
+        <v>397</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>397</v>
       </c>
     </row>
     <row r="38">
@@ -30356,16 +30356,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>71.8720344986678</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30377,7 +30377,7 @@
         <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,10 +30401,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
-        <v>124.2619859716246</v>
+        <v>397</v>
       </c>
       <c r="S39" t="n">
         <v>397</v>
@@ -30422,7 +30422,7 @@
         <v>397</v>
       </c>
       <c r="X39" t="n">
-        <v>397</v>
+        <v>239.9261063957067</v>
       </c>
       <c r="Y39" t="n">
         <v>397</v>
@@ -30441,7 +30441,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E40" t="n">
         <v>397</v>
@@ -30450,10 +30450,10 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
+        <v>244.3820695628415</v>
+      </c>
+      <c r="H40" t="n">
         <v>397</v>
-      </c>
-      <c r="H40" t="n">
-        <v>222.8870933147334</v>
       </c>
       <c r="I40" t="n">
         <v>397</v>
@@ -30489,22 +30489,22 @@
         <v>350.8400534733473</v>
       </c>
       <c r="T40" t="n">
-        <v>343.9399640103761</v>
+        <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
-        <v>150.9222929138022</v>
+        <v>237.0387846714448</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>397</v>
       </c>
       <c r="W40" t="n">
-        <v>397</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="41">
@@ -30611,7 +30611,7 @@
         <v>293</v>
       </c>
       <c r="H42" t="n">
-        <v>293</v>
+        <v>290.6132265545664</v>
       </c>
       <c r="I42" t="n">
         <v>189.9476123064429</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>69.92675579599782</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
         <v>293</v>
@@ -30848,7 +30848,7 @@
         <v>293</v>
       </c>
       <c r="H45" t="n">
-        <v>293</v>
+        <v>290.6132265545664</v>
       </c>
       <c r="I45" t="n">
         <v>189.9476123064429</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579599782</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34743,13 +34743,13 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824119</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>306.7289592406477</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
@@ -34761,10 +34761,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>374</v>
       </c>
       <c r="Q2" t="n">
-        <v>183.3412755627363</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -34892,16 +34892,16 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>150.6445354266185</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8023162586008343</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.83199570698063</v>
       </c>
       <c r="T4" t="n">
         <v>190.7613351330866</v>
@@ -34940,13 +34940,13 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,13 +34980,13 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M5" t="n">
         <v>183.3412755627362</v>
@@ -34995,7 +34995,7 @@
         <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>58.67867865278593</v>
@@ -35120,10 +35120,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>62.8982100014951</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
@@ -35138,7 +35138,7 @@
         <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>132.8490622644307</v>
@@ -35165,16 +35165,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>70.71701959344506</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>52.1599296482412</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512562</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
         <v>183.3412755627362</v>
@@ -35232,7 +35232,7 @@
         <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>58.67867865278593</v>
@@ -35357,19 +35357,19 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>51.00702550716294</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>40.76214231847804</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -35378,10 +35378,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,13 +35405,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,19 +35454,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K11" t="n">
+        <v>187.6734723618091</v>
+      </c>
+      <c r="L11" t="n">
+        <v>232.8255376884422</v>
+      </c>
+      <c r="M11" t="n">
         <v>655</v>
       </c>
-      <c r="L11" t="n">
-        <v>654.9999999999999</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
-        <v>200.7935788450894</v>
+        <v>607.3433266784076</v>
       </c>
       <c r="O11" t="n">
         <v>178.3365374610834</v>
@@ -35475,7 +35475,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q11" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35657,7 +35657,7 @@
         <v>71.55635456989245</v>
       </c>
       <c r="Y13" t="n">
-        <v>31.53464715053764</v>
+        <v>31.53464715053765</v>
       </c>
     </row>
     <row r="14">
@@ -35697,13 +35697,13 @@
         <v>654.9999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8255376884422</v>
+        <v>655</v>
       </c>
       <c r="M14" t="n">
-        <v>140.0167990402148</v>
+        <v>372.8423367286592</v>
       </c>
       <c r="N14" t="n">
-        <v>655.0000000000022</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
@@ -35931,16 +35931,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K17" t="n">
+        <v>187.673472361809</v>
+      </c>
+      <c r="L17" t="n">
+        <v>232.8255376884423</v>
+      </c>
+      <c r="M17" t="n">
         <v>655</v>
       </c>
-      <c r="L17" t="n">
-        <v>654.9999999999999</v>
-      </c>
-      <c r="M17" t="n">
-        <v>148.1470733148135</v>
-      </c>
       <c r="N17" t="n">
-        <v>655.0000000000024</v>
+        <v>435.2945687948378</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -35949,7 +35949,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36119,7 +36119,7 @@
         <v>111.8031384117751</v>
       </c>
       <c r="U19" t="n">
-        <v>168.0777070861981</v>
+        <v>168.0777070861978</v>
       </c>
       <c r="V19" t="n">
         <v>119.8296897837838</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K20" t="n">
+        <v>655</v>
+      </c>
+      <c r="L20" t="n">
         <v>654.9999999999999</v>
       </c>
-      <c r="L20" t="n">
-        <v>372.8423367286566</v>
-      </c>
       <c r="M20" t="n">
-        <v>655.0000000000027</v>
+        <v>148.1470733148158</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>655</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>238.324835913944</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
         <v>655</v>
       </c>
       <c r="L23" t="n">
+        <v>654.9999999999999</v>
+      </c>
+      <c r="M23" t="n">
+        <v>148.1470733148158</v>
+      </c>
+      <c r="N23" t="n">
         <v>655</v>
-      </c>
-      <c r="M23" t="n">
-        <v>655.0000000000025</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
@@ -36645,13 +36645,13 @@
         <v>187.6734723618091</v>
       </c>
       <c r="L26" t="n">
-        <v>655</v>
+        <v>655.000000000002</v>
       </c>
       <c r="M26" t="n">
-        <v>655.0000000000001</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N26" t="n">
-        <v>185.1688643668497</v>
+        <v>185.1688643668543</v>
       </c>
       <c r="O26" t="n">
         <v>178.3365374610834</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,16 +36879,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>187.673472361809</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="L29" t="n">
-        <v>654.9999999999999</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000005</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N29" t="n">
-        <v>13.12010648327964</v>
+        <v>570.3215356263778</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
@@ -36897,7 +36897,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q29" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37113,19 +37113,19 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>654.9999999999999</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="L32" t="n">
-        <v>655</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M32" t="n">
-        <v>372.8423367286592</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>570.3215356263778</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
@@ -37313,7 +37313,7 @@
         <v>92.62719016129032</v>
       </c>
       <c r="X34" t="n">
-        <v>71.5563545698932</v>
+        <v>71.55635456989245</v>
       </c>
       <c r="Y34" t="n">
         <v>31.53464715053764</v>
@@ -37356,13 +37356,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
         <v>374</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>206.0015986181083</v>
       </c>
       <c r="O35" t="n">
         <v>178.3365374610834</v>
@@ -37371,7 +37371,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>206.0015986180996</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37438,10 +37438,10 @@
         <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
-        <v>286.9650421645043</v>
+        <v>254.1901113963907</v>
       </c>
       <c r="N36" t="n">
-        <v>307.160421227325</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
         <v>46.59266649806909</v>
@@ -37484,34 +37484,34 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>109.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
         <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>116.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>55.84571637161132</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>152.6179304371585</v>
+        <v>137.7368680118811</v>
       </c>
       <c r="H37" t="n">
-        <v>174.1129066852666</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>185.3687343955783</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -37547,13 +37547,13 @@
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>170.6271901612903</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>149.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>109.5346471505376</v>
       </c>
     </row>
     <row r="38">
@@ -37593,19 +37593,19 @@
         <v>187.673472361809</v>
       </c>
       <c r="L38" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>206.0015986181083</v>
       </c>
       <c r="N38" t="n">
-        <v>222.2121162395067</v>
+        <v>374</v>
       </c>
       <c r="O38" t="n">
-        <v>374</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P38" t="n">
-        <v>374</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37678,10 +37678,10 @@
         <v>286.9650421645043</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>307.1604212273337</v>
       </c>
       <c r="O39" t="n">
-        <v>353.753087725394</v>
+        <v>46.59266649806909</v>
       </c>
       <c r="P39" t="n">
         <v>264.4060611184268</v>
@@ -37727,7 +37727,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E40" t="n">
         <v>116.0190951630435</v>
@@ -37736,10 +37736,10 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
         <v>240.2687738880785</v>
@@ -37775,22 +37775,22 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>136.7431024221511</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>86.11649175764259</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>197.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>170.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>90.1777625991308</v>
+        <v>374</v>
       </c>
       <c r="K41" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>296.1793612172393</v>
       </c>
       <c r="N41" t="n">
-        <v>222.2121162395067</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>374</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P41" t="n">
-        <v>374</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37909,19 +37909,19 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L42" t="n">
-        <v>57.40142568134173</v>
+        <v>374</v>
       </c>
       <c r="M42" t="n">
-        <v>286.9650421645043</v>
+        <v>169.2702674117983</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>353.753087725394</v>
+        <v>374</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37979,13 +37979,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I43" t="n">
-        <v>136.2687738880785</v>
+        <v>136.2687738880784</v>
       </c>
       <c r="J43" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K43" t="n">
-        <v>81.36873439557826</v>
+        <v>81.36873439557824</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -38012,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>85.80313841177508</v>
+        <v>85.80313841177507</v>
       </c>
       <c r="U43" t="n">
         <v>142.0777070861978</v>
@@ -38067,22 +38067,22 @@
         <v>187.673472361809</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M44" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>10.33813607918312</v>
+        <v>206.0015986181083</v>
       </c>
       <c r="O44" t="n">
-        <v>374</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P44" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38146,7 +38146,7 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L45" t="n">
-        <v>364.5618469086669</v>
+        <v>364.5618469086755</v>
       </c>
       <c r="M45" t="n">
         <v>286.9650421645043</v>
